--- a/examples/ghana-education-research/workspace/data/raw/ghana-demo-source-records.xlsx
+++ b/examples/ghana-education-research/workspace/data/raw/ghana-demo-source-records.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posts" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'posts'!$A$1:$AT$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'posts'!$A$1:$AT$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
+          <t>Ghana education advising American Spaces</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
+          <t>Ghana education advising American Spaces</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
+          <t>Ghana education advising American Spaces</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
+          <t>Ghana education advising American Spaces</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
+          <t>Ghana education advising American Spaces</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1368,138 +1368,8 @@
       </c>
       <c r="AT6" s="2" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>web</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>ciug-zjut-partnership</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>web:ciug-zjut-partnership</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>webpage</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="2" t="inlineStr"/>
-      <c r="V7" s="2" t="inlineStr"/>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>University of Ghana reports current CIUG board activity and work to strengthen its partnership with Zhejiang University of Technology.</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ug.edu.gh/news/ciug-board-meeting-charts-new-direction-2026-ug-and-zhejiang-university-technology-strengthen</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>Ghana education advising American Spaces university partnerships</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>manual_import</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>www.ug.edu.gh</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ug.edu.gh/news/ciug-board-meeting-charts-new-direction-2026-ug-and-zhejiang-university-technology-strengthen</t>
-        </is>
-      </c>
-      <c r="AF7" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-28T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="AG7" s="2" t="inlineStr">
-        <is>
-          <t>sugar-core-1.1</t>
-        </is>
-      </c>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="AJ7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="2" t="inlineStr">
-        <is>
-          <t>ciug-zjut-partnership</t>
-        </is>
-      </c>
-      <c r="AL7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ug.edu.gh/news/ciug-board-meeting-charts-new-direction-2026-ug-and-zhejiang-university-technology-strengthen</t>
-        </is>
-      </c>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AT7"/>
+  <autoFilter ref="A1:AT6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>